--- a/tests-dotnet/fixtures/service-interim/week2/Service Centre till 05 oct 2026/00_Service_Centre_Consolidation_Control.xlsx
+++ b/tests-dotnet/fixtures/service-interim/week2/Service Centre till 05 oct 2026/00_Service_Centre_Consolidation_Control.xlsx
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
